--- a/data/trans_dic/P36$huevo-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36$huevo-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón</t>
+          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,26</t>
+          <t>3,13; 6,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,21</t>
+          <t>3,99; 7,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,19; 12,68</t>
+          <t>8,2; 12,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,59</t>
+          <t>0,71; 2,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,38</t>
+          <t>1,04; 3,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,08; 10,3</t>
+          <t>6,09; 10,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,0</t>
+          <t>2,11; 3,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,83</t>
+          <t>2,83; 4,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 10,73</t>
+          <t>7,62; 10,76</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,12</t>
+          <t>3,22; 6,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,05</t>
+          <t>2,7; 5,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,46</t>
+          <t>8,5; 12,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,9</t>
+          <t>2,32; 4,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,29</t>
+          <t>0,78; 2,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 10,74</t>
+          <t>7,15; 10,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,99</t>
+          <t>3,04; 4,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,38</t>
+          <t>1,94; 3,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,34; 11,04</t>
+          <t>8,47; 11,09</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,23</t>
+          <t>2,31; 5,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,83</t>
+          <t>3,58; 6,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,34</t>
+          <t>1,83; 4,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,56</t>
+          <t>0,74; 2,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,8</t>
+          <t>1,99; 4,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,03</t>
+          <t>1,15; 3,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,6</t>
+          <t>1,8; 3,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 5,22</t>
+          <t>3,17; 5,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,24</t>
+          <t>1,7; 3,27</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,19</t>
+          <t>1,4; 3,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,44</t>
+          <t>2,07; 4,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,55</t>
+          <t>4,35; 7,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,67</t>
+          <t>1,04; 2,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,09</t>
+          <t>1,96; 4,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,9</t>
+          <t>3,79; 6,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,64</t>
+          <t>1,37; 2,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,93</t>
+          <t>2,29; 3,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,56</t>
+          <t>4,39; 6,45</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 4,34</t>
+          <t>2,95; 4,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 4,95</t>
+          <t>3,49; 4,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,27</t>
+          <t>6,58; 8,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,64</t>
+          <t>1,65; 2,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 2,94</t>
+          <t>1,8; 2,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,89</t>
+          <t>5,39; 7,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,28</t>
+          <t>2,43; 3,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,67</t>
+          <t>2,86; 3,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,1; 7,35</t>
+          <t>6,1; 7,32</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón</t>
+          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21559; 43398</t>
+          <t>21662; 43771</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27190; 50593</t>
+          <t>27989; 50668</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55133; 85350</t>
+          <t>55197; 86168</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5102; 17834</t>
+          <t>4905; 17527</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7065; 23558</t>
+          <t>7271; 24327</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40818; 69160</t>
+          <t>40889; 70101</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29677; 55232</t>
+          <t>29192; 55067</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38885; 67439</t>
+          <t>39482; 68935</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>103294; 144217</t>
+          <t>102468; 144718</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31103; 58656</t>
+          <t>30870; 59138</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26766; 51392</t>
+          <t>27441; 52637</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87420; 127266</t>
+          <t>86822; 126723</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23082; 47361</t>
+          <t>22441; 47978</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8165; 23577</t>
+          <t>8057; 23480</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73748; 111879</t>
+          <t>74479; 111321</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60173; 96056</t>
+          <t>58552; 95559</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39980; 69141</t>
+          <t>39775; 67565</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>172076; 227813</t>
+          <t>174774; 228880</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13654; 35446</t>
+          <t>15643; 37111</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26090; 51640</t>
+          <t>27032; 52209</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14689; 32884</t>
+          <t>13886; 33959</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5316; 17506</t>
+          <t>5040; 17688</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15464; 37289</t>
+          <t>15410; 37708</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8354; 23763</t>
+          <t>9001; 24295</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24012; 49030</t>
+          <t>24572; 49327</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47766; 80014</t>
+          <t>48544; 80753</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26483; 50076</t>
+          <t>26164; 50446</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13134; 30029</t>
+          <t>13195; 29681</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20488; 41960</t>
+          <t>19624; 41354</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41649; 70809</t>
+          <t>40826; 69459</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9818; 27667</t>
+          <t>10810; 27829</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20649; 42925</t>
+          <t>20587; 44222</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39531; 71994</t>
+          <t>39547; 70244</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26731; 52258</t>
+          <t>27153; 50842</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46271; 78384</t>
+          <t>45690; 78476</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89026; 129966</t>
+          <t>86875; 127821</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>99597; 142048</t>
+          <t>96616; 143034</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>119929; 169409</t>
+          <t>119496; 167878</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>223198; 280357</t>
+          <t>223018; 285211</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55194; 89177</t>
+          <t>55733; 89664</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>65029; 104497</t>
+          <t>64011; 102198</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>185120; 243954</t>
+          <t>190784; 249273</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>162591; 218052</t>
+          <t>161452; 216795</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>197467; 256117</t>
+          <t>199328; 258091</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>422647; 509481</t>
+          <t>422754; 507743</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$huevo-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36$huevo-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,32</t>
+          <t>2,98; 6,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,22</t>
+          <t>3,94; 7,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,2; 12,8</t>
+          <t>8,25; 12,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,55</t>
+          <t>0,71; 2,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,49</t>
+          <t>1,05; 3,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 10,44</t>
+          <t>6,19; 10,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,99</t>
+          <t>2,17; 3,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,93</t>
+          <t>2,79; 4,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,62; 10,76</t>
+          <t>7,74; 10,91</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,17</t>
+          <t>3,17; 6,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,17</t>
+          <t>2,62; 5,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,5; 12,41</t>
+          <t>8,4; 12,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,96</t>
+          <t>2,32; 4,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,28</t>
+          <t>0,79; 2,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 10,68</t>
+          <t>7,06; 10,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 4,96</t>
+          <t>3,06; 5,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,3</t>
+          <t>1,9; 3,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,47; 11,09</t>
+          <t>8,41; 10,97</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,48</t>
+          <t>2,24; 5,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,91</t>
+          <t>3,58; 6,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,48</t>
+          <t>1,93; 4,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,59</t>
+          <t>0,75; 2,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,86</t>
+          <t>1,98; 4,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,09</t>
+          <t>1,16; 3,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,62</t>
+          <t>1,69; 3,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,27</t>
+          <t>3,08; 5,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,27</t>
+          <t>1,7; 3,22</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,16</t>
+          <t>1,4; 3,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,37</t>
+          <t>2,19; 4,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 7,41</t>
+          <t>4,46; 7,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,69</t>
+          <t>0,97; 2,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,21</t>
+          <t>1,92; 4,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,74</t>
+          <t>3,86; 6,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,57</t>
+          <t>1,37; 2,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,93</t>
+          <t>2,31; 3,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,45</t>
+          <t>4,39; 6,5</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,37</t>
+          <t>2,94; 4,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,91</t>
+          <t>3,56; 4,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,41</t>
+          <t>6,61; 8,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,66</t>
+          <t>1,64; 2,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,88</t>
+          <t>1,85; 2,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,39; 7,04</t>
+          <t>5,21; 6,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,26</t>
+          <t>2,44; 3,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,86; 3,7</t>
+          <t>2,83; 3,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,1; 7,32</t>
+          <t>6,16; 7,39</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21662; 43771</t>
+          <t>20659; 43729</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27989; 50668</t>
+          <t>27632; 51555</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55197; 86168</t>
+          <t>55546; 85897</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4905; 17527</t>
+          <t>4859; 17630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7271; 24327</t>
+          <t>7315; 23410</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40889; 70101</t>
+          <t>41590; 70603</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29192; 55067</t>
+          <t>29966; 54274</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39482; 68935</t>
+          <t>38945; 67195</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>102468; 144718</t>
+          <t>104039; 146661</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30870; 59138</t>
+          <t>30416; 58879</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27441; 52637</t>
+          <t>26685; 51417</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86822; 126723</t>
+          <t>85749; 126700</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22441; 47978</t>
+          <t>22491; 46889</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8057; 23480</t>
+          <t>8163; 23230</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74479; 111321</t>
+          <t>73573; 111935</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58552; 95559</t>
+          <t>59039; 96331</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39775; 67565</t>
+          <t>38915; 68751</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>174774; 228880</t>
+          <t>173609; 226271</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15643; 37111</t>
+          <t>15177; 35793</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27032; 52209</t>
+          <t>27081; 52720</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13886; 33959</t>
+          <t>14632; 33703</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5040; 17688</t>
+          <t>5162; 18069</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15410; 37708</t>
+          <t>15354; 37499</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9001; 24295</t>
+          <t>9095; 24945</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24572; 49327</t>
+          <t>22950; 47600</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48544; 80753</t>
+          <t>47189; 79475</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26164; 50446</t>
+          <t>26315; 49700</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13195; 29681</t>
+          <t>13209; 30810</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19624; 41354</t>
+          <t>20729; 42760</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40826; 69459</t>
+          <t>41771; 70990</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10810; 27829</t>
+          <t>10007; 28294</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20587; 44222</t>
+          <t>20203; 42525</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39547; 70244</t>
+          <t>40210; 70846</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27153; 50842</t>
+          <t>27058; 50365</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45690; 78476</t>
+          <t>46070; 77007</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>86875; 127821</t>
+          <t>86936; 128640</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>96616; 143034</t>
+          <t>96059; 140992</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>119496; 167878</t>
+          <t>121903; 167997</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>223018; 285211</t>
+          <t>224167; 283870</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55733; 89664</t>
+          <t>55299; 88606</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>64011; 102198</t>
+          <t>65849; 104174</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>190784; 249273</t>
+          <t>184554; 243990</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>161452; 216795</t>
+          <t>162356; 215852</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>199328; 258091</t>
+          <t>197247; 260043</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>422754; 507743</t>
+          <t>427114; 512394</t>
         </is>
       </c>
     </row>
